--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/123.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/123.xlsx
@@ -426,13 +426,13 @@
         <v>-18.81597213025158</v>
       </c>
       <c r="E2">
-        <v>-10.63832491484486</v>
+        <v>-13.27595271450849</v>
       </c>
       <c r="F2">
-        <v>-2.29417609481178</v>
+        <v>-2.004375072411985</v>
       </c>
       <c r="G2">
-        <v>-7.875330945114486</v>
+        <v>-8.014031461653774</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-18.55993328167052</v>
       </c>
       <c r="E3">
-        <v>-10.85675133013083</v>
+        <v>-12.10672789657205</v>
       </c>
       <c r="F3">
-        <v>-1.908939692302857</v>
+        <v>-1.881841309455076</v>
       </c>
       <c r="G3">
-        <v>-7.646813550828519</v>
+        <v>-7.27045087551709</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-18.2952423009927</v>
       </c>
       <c r="E4">
-        <v>-11.76855504310125</v>
+        <v>-12.99876482049899</v>
       </c>
       <c r="F4">
-        <v>-1.861846177086302</v>
+        <v>-2.143136552789735</v>
       </c>
       <c r="G4">
-        <v>-7.458080967950818</v>
+        <v>-6.812786092405742</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-18.03160854724985</v>
       </c>
       <c r="E5">
-        <v>-12.24949256813787</v>
+        <v>-14.05084707280501</v>
       </c>
       <c r="F5">
-        <v>-2.140262117902021</v>
+        <v>-2.123069352456918</v>
       </c>
       <c r="G5">
-        <v>-6.254922646533629</v>
+        <v>-7.031807631498676</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-17.76369829291664</v>
       </c>
       <c r="E6">
-        <v>-13.16070305101328</v>
+        <v>-14.87828531501253</v>
       </c>
       <c r="F6">
-        <v>-1.681348233485901</v>
+        <v>-1.762558888554156</v>
       </c>
       <c r="G6">
-        <v>-5.808640421011994</v>
+        <v>-6.412211283207172</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-17.49932902435814</v>
       </c>
       <c r="E7">
-        <v>-14.24452084916506</v>
+        <v>-17.2765923203188</v>
       </c>
       <c r="F7">
-        <v>-2.037189190339082</v>
+        <v>-1.389083646430179</v>
       </c>
       <c r="G7">
-        <v>-5.713717962518817</v>
+        <v>-4.890154319649111</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-17.24679362802289</v>
       </c>
       <c r="E8">
-        <v>-14.31891914863707</v>
+        <v>-15.16859219822225</v>
       </c>
       <c r="F8">
-        <v>-1.722711931377291</v>
+        <v>-1.68134492001629</v>
       </c>
       <c r="G8">
-        <v>-4.149628550784271</v>
+        <v>-5.292628956130599</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-17.00716179853597</v>
       </c>
       <c r="E9">
-        <v>-14.90091409962886</v>
+        <v>-16.8515135221668</v>
       </c>
       <c r="F9">
-        <v>-2.02206237319656</v>
+        <v>-1.598057547869216</v>
       </c>
       <c r="G9">
-        <v>-4.659395851038042</v>
+        <v>-4.240075423070364</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-16.77852129984105</v>
       </c>
       <c r="E10">
-        <v>-15.29216519694356</v>
+        <v>-17.21163588915277</v>
       </c>
       <c r="F10">
-        <v>-1.722730983827556</v>
+        <v>-1.797735510314037</v>
       </c>
       <c r="G10">
-        <v>-3.671895816615357</v>
+        <v>-3.047344823769091</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-16.55811732486351</v>
       </c>
       <c r="E11">
-        <v>-15.95493453881017</v>
+        <v>-18.03811409487067</v>
       </c>
       <c r="F11">
-        <v>-1.413846033202065</v>
+        <v>-1.238114515637372</v>
       </c>
       <c r="G11">
-        <v>-3.224488132098833</v>
+        <v>-3.597500680198067</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-16.33632367773725</v>
       </c>
       <c r="E12">
-        <v>-17.44202653276701</v>
+        <v>-19.21137831162195</v>
       </c>
       <c r="F12">
-        <v>-1.398073917852762</v>
+        <v>-0.8363836614039042</v>
       </c>
       <c r="G12">
-        <v>-2.64606127071368</v>
+        <v>-3.003481453962434</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-16.11024690398106</v>
       </c>
       <c r="E13">
-        <v>-17.70192924148924</v>
+        <v>-17.98869938649897</v>
       </c>
       <c r="F13">
-        <v>-1.400241755345888</v>
+        <v>-0.4186230695588631</v>
       </c>
       <c r="G13">
-        <v>-1.76696623417193</v>
+        <v>-1.421437197854605</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-15.88973787837298</v>
       </c>
       <c r="E14">
-        <v>-17.80399198867411</v>
+        <v>-20.9028041097529</v>
       </c>
       <c r="F14">
-        <v>-1.488300523733087</v>
+        <v>-0.3510779915345914</v>
       </c>
       <c r="G14">
-        <v>-1.430161965981168</v>
+        <v>-2.843708932568392</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-15.67474513336282</v>
       </c>
       <c r="E15">
-        <v>-18.92378398434282</v>
+        <v>-22.61847988619492</v>
       </c>
       <c r="F15">
-        <v>-1.631726540956002</v>
+        <v>-0.9402269706514474</v>
       </c>
       <c r="G15">
-        <v>-1.401927054462146</v>
+        <v>-1.136364668770048</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-15.4642845790016</v>
       </c>
       <c r="E16">
-        <v>-19.83429708222105</v>
+        <v>-23.02834301168115</v>
       </c>
       <c r="F16">
-        <v>-1.251878668402289</v>
+        <v>-0.335664559270701</v>
       </c>
       <c r="G16">
-        <v>-0.9569605987858485</v>
+        <v>-1.922683165718498</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-15.25649682750729</v>
       </c>
       <c r="E17">
-        <v>-21.48762482852547</v>
+        <v>-23.27338779718421</v>
       </c>
       <c r="F17">
-        <v>-1.22378375956894</v>
+        <v>0.1223704273310492</v>
       </c>
       <c r="G17">
-        <v>-1.166633937655925</v>
+        <v>-0.6958377058636785</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-15.04357220584679</v>
       </c>
       <c r="E18">
-        <v>-21.9825009965577</v>
+        <v>-23.88209621634724</v>
       </c>
       <c r="F18">
-        <v>-1.002081992985889</v>
+        <v>-0.2641275787323385</v>
       </c>
       <c r="G18">
-        <v>-0.1345092900247927</v>
+        <v>-0.1154453927644189</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-14.81930600139209</v>
       </c>
       <c r="E19">
-        <v>-21.27666133840414</v>
+        <v>-23.75802508548509</v>
       </c>
       <c r="F19">
-        <v>-1.206969558026916</v>
+        <v>-0.2002728774875386</v>
       </c>
       <c r="G19">
-        <v>0.1847470052660593</v>
+        <v>0.1279129666349174</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-14.5873395264326</v>
       </c>
       <c r="E20">
-        <v>-22.64062412409243</v>
+        <v>-24.72644830897341</v>
       </c>
       <c r="F20">
-        <v>-0.8340095604274808</v>
+        <v>0.07789869494435496</v>
       </c>
       <c r="G20">
-        <v>1.142748857869336</v>
+        <v>0.9409242009694507</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-14.34794974993415</v>
       </c>
       <c r="E21">
-        <v>-22.72781083416211</v>
+        <v>-26.43945228575091</v>
       </c>
       <c r="F21">
-        <v>-0.6761707787632574</v>
+        <v>0.04975905427125575</v>
       </c>
       <c r="G21">
-        <v>0.6703743585069961</v>
+        <v>1.267011999547067</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-14.09966635289604</v>
       </c>
       <c r="E22">
-        <v>-23.27220586546821</v>
+        <v>-26.71426273090638</v>
       </c>
       <c r="F22">
-        <v>-0.4455267860669855</v>
+        <v>-0.4413882625225991</v>
       </c>
       <c r="G22">
-        <v>0.8285161127859936</v>
+        <v>1.111544440839016</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-13.84233355268661</v>
       </c>
       <c r="E23">
-        <v>-23.92759379470231</v>
+        <v>-27.15121518790649</v>
       </c>
       <c r="F23">
-        <v>-0.2965225427536188</v>
+        <v>-0.1180118525525337</v>
       </c>
       <c r="G23">
-        <v>1.166147248809736</v>
+        <v>2.982477286705037</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-13.57538356725463</v>
       </c>
       <c r="E24">
-        <v>-24.61448178913376</v>
+        <v>-28.9794642997052</v>
       </c>
       <c r="F24">
-        <v>-0.3039654238677724</v>
+        <v>0.4236095468287006</v>
       </c>
       <c r="G24">
-        <v>1.63973580014907</v>
+        <v>3.252449634173029</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-13.29850944308272</v>
       </c>
       <c r="E25">
-        <v>-25.13566839115055</v>
+        <v>-28.78175565300431</v>
       </c>
       <c r="F25">
-        <v>-0.0421474807019466</v>
+        <v>-0.04658918671575755</v>
       </c>
       <c r="G25">
-        <v>1.260502055973128</v>
+        <v>2.432019557892591</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-13.02108226048605</v>
       </c>
       <c r="E26">
-        <v>-25.0185077116241</v>
+        <v>-27.30422779615167</v>
       </c>
       <c r="F26">
-        <v>-0.3603051760343751</v>
+        <v>0.02789346830696</v>
       </c>
       <c r="G26">
-        <v>2.676824935999643</v>
+        <v>2.463555378300414</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-12.7549696131646</v>
       </c>
       <c r="E27">
-        <v>-26.00394441195924</v>
+        <v>-27.97575973522311</v>
       </c>
       <c r="F27">
-        <v>-0.1157644917887387</v>
+        <v>-0.1080788990255648</v>
       </c>
       <c r="G27">
-        <v>2.217001109102179</v>
+        <v>5.169805202662073</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-12.50627981746407</v>
       </c>
       <c r="E28">
-        <v>-24.89630231205311</v>
+        <v>-27.07687123012257</v>
       </c>
       <c r="F28">
-        <v>-0.2975348077198398</v>
+        <v>0.2271489633763531</v>
       </c>
       <c r="G28">
-        <v>2.507654996059351</v>
+        <v>3.850655699118514</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-12.27939918919981</v>
       </c>
       <c r="E29">
-        <v>-25.60965018011138</v>
+        <v>-29.57737683683394</v>
       </c>
       <c r="F29">
-        <v>-0.139292611130453</v>
+        <v>-0.2481806778610452</v>
       </c>
       <c r="G29">
-        <v>2.272437347348998</v>
+        <v>2.945474951179178</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-12.07605869300995</v>
       </c>
       <c r="E30">
-        <v>-26.07735550409759</v>
+        <v>-28.6762467370996</v>
       </c>
       <c r="F30">
-        <v>-0.1130631856882095</v>
+        <v>0.1986763190073285</v>
       </c>
       <c r="G30">
-        <v>2.28435802527446</v>
+        <v>3.956963996422963</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.89240385938482</v>
       </c>
       <c r="E31">
-        <v>-24.62366100594731</v>
+        <v>-28.09463217792446</v>
       </c>
       <c r="F31">
-        <v>-0.4045714733051751</v>
+        <v>-0.1659527876221523</v>
       </c>
       <c r="G31">
-        <v>2.684092841753813</v>
+        <v>3.934202162465096</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.72891784749522</v>
       </c>
       <c r="E32">
-        <v>-24.98623780584544</v>
+        <v>-27.44567015330724</v>
       </c>
       <c r="F32">
-        <v>-0.1071792920261246</v>
+        <v>0.02871852224014831</v>
       </c>
       <c r="G32">
-        <v>2.785315245641123</v>
+        <v>3.453844451048627</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.59285522850475</v>
       </c>
       <c r="E33">
-        <v>-25.04886660137153</v>
+        <v>-28.0719852794121</v>
       </c>
       <c r="F33">
-        <v>-0.07893527706027265</v>
+        <v>-0.193656707041379</v>
       </c>
       <c r="G33">
-        <v>1.907933006753403</v>
+        <v>2.654141851359201</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.48323105697323</v>
       </c>
       <c r="E34">
-        <v>-23.89150185686117</v>
+        <v>-27.6481427546642</v>
       </c>
       <c r="F34">
-        <v>-0.1777081494352801</v>
+        <v>0.200521093213363</v>
       </c>
       <c r="G34">
-        <v>1.884262274423569</v>
+        <v>2.591519737897199</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.39774752219977</v>
       </c>
       <c r="E35">
-        <v>-23.6306255262273</v>
+        <v>-26.68088787746985</v>
       </c>
       <c r="F35">
-        <v>-0.0416454900558501</v>
+        <v>-0.0516993852236277</v>
       </c>
       <c r="G35">
-        <v>1.903231016258718</v>
+        <v>3.304775274381494</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.33369696688288</v>
       </c>
       <c r="E36">
-        <v>-23.30916727031881</v>
+        <v>-23.88185167875083</v>
       </c>
       <c r="F36">
-        <v>-0.1909562293082526</v>
+        <v>0.05963402208002866</v>
       </c>
       <c r="G36">
-        <v>2.307612042466245</v>
+        <v>2.157056472432684</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.28370117586696</v>
       </c>
       <c r="E37">
-        <v>-22.58764550667669</v>
+        <v>-24.63956047818824</v>
       </c>
       <c r="F37">
-        <v>-0.3994935811260141</v>
+        <v>0.2780140353778539</v>
       </c>
       <c r="G37">
-        <v>1.4393581619569</v>
+        <v>2.10915720010791</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.24452501941789</v>
       </c>
       <c r="E38">
-        <v>-21.98590188053745</v>
+        <v>-25.5164994697736</v>
       </c>
       <c r="F38">
-        <v>-0.07601859543501559</v>
+        <v>0.7021298619371728</v>
       </c>
       <c r="G38">
-        <v>1.151073316965647</v>
+        <v>2.609697705336523</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.22134163195118</v>
       </c>
       <c r="E39">
-        <v>-22.0648648818092</v>
+        <v>-23.12361304785452</v>
       </c>
       <c r="F39">
-        <v>-0.210001224266016</v>
+        <v>0.2709720840866554</v>
       </c>
       <c r="G39">
-        <v>1.48427152266258</v>
+        <v>0.3819418585455678</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.2165906141276</v>
       </c>
       <c r="E40">
-        <v>-20.65049565194154</v>
+        <v>-22.3182556449084</v>
       </c>
       <c r="F40">
-        <v>-0.01124357800570544</v>
+        <v>0.1897059284024126</v>
       </c>
       <c r="G40">
-        <v>1.243587358834191</v>
+        <v>1.472032566245851</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.23175543855802</v>
       </c>
       <c r="E41">
-        <v>-21.12690017449647</v>
+        <v>-23.31951483342634</v>
       </c>
       <c r="F41">
-        <v>-0.1436953838763324</v>
+        <v>0.2880588185042007</v>
       </c>
       <c r="G41">
-        <v>0.6231510178234677</v>
+        <v>1.783112057410566</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.26842895720516</v>
       </c>
       <c r="E42">
-        <v>-19.63280263124976</v>
+        <v>-20.98794847804512</v>
       </c>
       <c r="F42">
-        <v>-0.09331490680546926</v>
+        <v>0.5961725590776853</v>
       </c>
       <c r="G42">
-        <v>0.8600453707506979</v>
+        <v>0.8556944709628742</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.32470731968643</v>
       </c>
       <c r="E43">
-        <v>-19.37945715289064</v>
+        <v>-21.26732815347433</v>
       </c>
       <c r="F43">
-        <v>-0.2548167291248721</v>
+        <v>0.5340184961108327</v>
       </c>
       <c r="G43">
-        <v>0.7721578512809711</v>
+        <v>0.06217041146988302</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.39737764007311</v>
       </c>
       <c r="E44">
-        <v>-18.51190115944917</v>
+        <v>-19.64277885948866</v>
       </c>
       <c r="F44">
-        <v>0.1795360617982431</v>
+        <v>0.3324087808826834</v>
       </c>
       <c r="G44">
-        <v>0.3735222440240327</v>
+        <v>0.1698535406077397</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.48971440050274</v>
       </c>
       <c r="E45">
-        <v>-17.39986191128159</v>
+        <v>-19.13845629467643</v>
       </c>
       <c r="F45">
-        <v>0.3000925117646692</v>
+        <v>1.048546482848704</v>
       </c>
       <c r="G45">
-        <v>-0.1201736330315787</v>
+        <v>-0.6741980496791407</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.60374839252002</v>
       </c>
       <c r="E46">
-        <v>-17.24225290191863</v>
+        <v>-19.12767399806417</v>
       </c>
       <c r="F46">
-        <v>0.2731564889278376</v>
+        <v>0.495754549040718</v>
       </c>
       <c r="G46">
-        <v>0.6693965544822815</v>
+        <v>0.9716331535442938</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-11.73681240408013</v>
       </c>
       <c r="E47">
-        <v>-17.15541941282155</v>
+        <v>-18.93673089153075</v>
       </c>
       <c r="F47">
-        <v>0.03909051049060092</v>
+        <v>0.7093018669106109</v>
       </c>
       <c r="G47">
-        <v>-0.08259052128969895</v>
+        <v>-0.3125057159599902</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-11.88482428149659</v>
       </c>
       <c r="E48">
-        <v>-15.74506693939869</v>
+        <v>-17.46808337220715</v>
       </c>
       <c r="F48">
-        <v>0.3531204510548795</v>
+        <v>1.169675334690464</v>
       </c>
       <c r="G48">
-        <v>-0.4800416075636779</v>
+        <v>-0.3118199406540662</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-12.04146462919918</v>
       </c>
       <c r="E49">
-        <v>-14.35968900012813</v>
+        <v>-19.02015443970005</v>
       </c>
       <c r="F49">
-        <v>0.3253320381605673</v>
+        <v>0.8976593604287737</v>
       </c>
       <c r="G49">
-        <v>-0.3813227757262242</v>
+        <v>-1.785770914929108</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-12.19550329449199</v>
       </c>
       <c r="E50">
-        <v>-15.04890463019953</v>
+        <v>-15.50050217214045</v>
       </c>
       <c r="F50">
-        <v>0.5697716615830622</v>
+        <v>0.7994978231970323</v>
       </c>
       <c r="G50">
-        <v>-0.681091896175534</v>
+        <v>-0.7962463668042463</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-12.34348906960827</v>
       </c>
       <c r="E51">
-        <v>-14.62311486162832</v>
+        <v>-14.47750177991168</v>
       </c>
       <c r="F51">
-        <v>0.4276801442460574</v>
+        <v>0.9466688894480036</v>
       </c>
       <c r="G51">
-        <v>-0.7491411500968579</v>
+        <v>-1.910099681038028</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-12.48643679484296</v>
       </c>
       <c r="E52">
-        <v>-13.03988336448863</v>
+        <v>-14.99890122020683</v>
       </c>
       <c r="F52">
-        <v>0.1899254457641545</v>
+        <v>0.9792982814442762</v>
       </c>
       <c r="G52">
-        <v>-0.9777471373649307</v>
+        <v>-2.113056359375921</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-12.62112058536598</v>
       </c>
       <c r="E53">
-        <v>-12.75034179338621</v>
+        <v>-14.50791048287319</v>
       </c>
       <c r="F53">
-        <v>0.7773373384373399</v>
+        <v>0.4832387459518203</v>
       </c>
       <c r="G53">
-        <v>-1.410340106540563</v>
+        <v>-2.106264230747871</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-12.74471690111283</v>
       </c>
       <c r="E54">
-        <v>-13.0747571428217</v>
+        <v>-12.66007119251731</v>
       </c>
       <c r="F54">
-        <v>0.560992623848193</v>
+        <v>1.265641698304787</v>
       </c>
       <c r="G54">
-        <v>-2.064261313565419</v>
+        <v>-1.360449132729206</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-12.854630114633</v>
       </c>
       <c r="E55">
-        <v>-11.09526605611483</v>
+        <v>-12.4203700063433</v>
       </c>
       <c r="F55">
-        <v>0.5049138074134721</v>
+        <v>0.4025888956152604</v>
       </c>
       <c r="G55">
-        <v>-2.336517391238785</v>
+        <v>-2.372089114164725</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-12.94310057107935</v>
       </c>
       <c r="E56">
-        <v>-11.74387485975945</v>
+        <v>-12.15511464134401</v>
       </c>
       <c r="F56">
-        <v>0.5619568435050517</v>
+        <v>0.6951268439139058</v>
       </c>
       <c r="G56">
-        <v>-2.052642508023425</v>
+        <v>-3.218020844405167</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-13.00825408173924</v>
       </c>
       <c r="E57">
-        <v>-10.73129901469634</v>
+        <v>-12.30992958224423</v>
       </c>
       <c r="F57">
-        <v>0.6691550407339328</v>
+        <v>0.1084803627209071</v>
       </c>
       <c r="G57">
-        <v>-2.454204964911388</v>
+        <v>-2.418757928404707</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-13.05487175909284</v>
       </c>
       <c r="E58">
-        <v>-10.7335768371222</v>
+        <v>-10.78511087132949</v>
       </c>
       <c r="F58">
-        <v>0.372115743968475</v>
+        <v>1.082507889628678</v>
       </c>
       <c r="G58">
-        <v>-2.809708914769426</v>
+        <v>-2.197049068854587</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-13.08343812179739</v>
       </c>
       <c r="E59">
-        <v>-10.68066614681658</v>
+        <v>-11.0306039757593</v>
       </c>
       <c r="F59">
-        <v>0.7108890188543747</v>
+        <v>0.7275723383467568</v>
       </c>
       <c r="G59">
-        <v>-3.265086686453842</v>
+        <v>-3.53242749423116</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-13.09321110017829</v>
       </c>
       <c r="E60">
-        <v>-11.25084630912235</v>
+        <v>-9.933178113214478</v>
       </c>
       <c r="F60">
-        <v>0.428785186361392</v>
+        <v>0.6200900110987154</v>
       </c>
       <c r="G60">
-        <v>-3.247184341625512</v>
+        <v>-3.23390195675288</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-13.08363006225952</v>
       </c>
       <c r="E61">
-        <v>-10.08704207457309</v>
+        <v>-10.48427528605193</v>
       </c>
       <c r="F61">
-        <v>0.4436701202222962</v>
+        <v>0.9057491964845137</v>
       </c>
       <c r="G61">
-        <v>-3.718246352364074</v>
+        <v>-3.542563187628284</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-13.05131393615823</v>
       </c>
       <c r="E62">
-        <v>-10.20969579307084</v>
+        <v>-10.51185822123265</v>
       </c>
       <c r="F62">
-        <v>0.4965067066424599</v>
+        <v>1.018213325292991</v>
       </c>
       <c r="G62">
-        <v>-3.921150531157016</v>
+        <v>-3.23567053517342</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-12.99399593582498</v>
       </c>
       <c r="E63">
-        <v>-10.21621679564189</v>
+        <v>-10.22445408986184</v>
       </c>
       <c r="F63">
-        <v>0.7019293970256953</v>
+        <v>-0.02524712895003109</v>
       </c>
       <c r="G63">
-        <v>-3.927227353485107</v>
+        <v>-3.93690367586391</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-12.91749147006039</v>
       </c>
       <c r="E64">
-        <v>-9.354647444838559</v>
+        <v>-12.15862420869995</v>
       </c>
       <c r="F64">
-        <v>0.3279960677279705</v>
+        <v>0.479963381241151</v>
       </c>
       <c r="G64">
-        <v>-3.361603818624908</v>
+        <v>-3.781856113515468</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-12.82747025869033</v>
       </c>
       <c r="E65">
-        <v>-9.145037968445521</v>
+        <v>-10.98353954539759</v>
       </c>
       <c r="F65">
-        <v>0.1928644933092871</v>
+        <v>0.6777973978473402</v>
       </c>
       <c r="G65">
-        <v>-3.999581570092423</v>
+        <v>-4.790598776313998</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-12.72630508813949</v>
       </c>
       <c r="E66">
-        <v>-10.04044860550817</v>
+        <v>-9.636237015583516</v>
       </c>
       <c r="F66">
-        <v>0.5515981091330439</v>
+        <v>0.02175526585221567</v>
       </c>
       <c r="G66">
-        <v>-4.055828270064424</v>
+        <v>-5.560822881513372</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-12.61594797269752</v>
       </c>
       <c r="E67">
-        <v>-8.976361368607815</v>
+        <v>-9.857697508454628</v>
       </c>
       <c r="F67">
-        <v>0.2762719787297666</v>
+        <v>-0.04058932161728073</v>
       </c>
       <c r="G67">
-        <v>-4.842963791181177</v>
+        <v>-4.869571216806714</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-12.49650898263525</v>
       </c>
       <c r="E68">
-        <v>-9.814441524733361</v>
+        <v>-8.713098532171898</v>
       </c>
       <c r="F68">
-        <v>0.18610998550686</v>
+        <v>0.1880881268647452</v>
       </c>
       <c r="G68">
-        <v>-4.299527876505943</v>
+        <v>-4.589778173211303</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-12.36444781066222</v>
       </c>
       <c r="E69">
-        <v>-9.316440709635843</v>
+        <v>-9.458394784354287</v>
       </c>
       <c r="F69">
-        <v>0.2861204387816499</v>
+        <v>0.4593221222981929</v>
       </c>
       <c r="G69">
-        <v>-4.662572073507584</v>
+        <v>-4.963207436448587</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-12.22230560179688</v>
       </c>
       <c r="E70">
-        <v>-9.011108349668669</v>
+        <v>-9.013970345241518</v>
       </c>
       <c r="F70">
-        <v>0.326498379463709</v>
+        <v>-0.3238976003139341</v>
       </c>
       <c r="G70">
-        <v>-4.579173265131178</v>
+        <v>-3.338546674726691</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-12.07719551359572</v>
       </c>
       <c r="E71">
-        <v>-9.558057440315096</v>
+        <v>-8.40843638635786</v>
       </c>
       <c r="F71">
-        <v>0.396533529900796</v>
+        <v>0.5291054490448288</v>
       </c>
       <c r="G71">
-        <v>-4.001983424273936</v>
+        <v>-4.251720478384833</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-11.93070505852402</v>
       </c>
       <c r="E72">
-        <v>-9.428742336552061</v>
+        <v>-8.53781941723101</v>
       </c>
       <c r="F72">
-        <v>0.2126086303550133</v>
+        <v>0.3271064011373638</v>
       </c>
       <c r="G72">
-        <v>-4.160971733715271</v>
+        <v>-4.108107973171057</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-11.78399334514176</v>
       </c>
       <c r="E73">
-        <v>-9.052869936967406</v>
+        <v>-10.36783010541869</v>
       </c>
       <c r="F73">
-        <v>0.5189281271340341</v>
+        <v>-0.4681080814673</v>
       </c>
       <c r="G73">
-        <v>-3.91521808257754</v>
+        <v>-3.748322029177944</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-11.63788208909797</v>
       </c>
       <c r="E74">
-        <v>-9.957803954868188</v>
+        <v>-10.8292182081642</v>
       </c>
       <c r="F74">
-        <v>0.470960684307526</v>
+        <v>-0.2635013329758221</v>
       </c>
       <c r="G74">
-        <v>-4.369030711578101</v>
+        <v>-4.787045213365119</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-11.48822040068785</v>
       </c>
       <c r="E75">
-        <v>-10.18979767828114</v>
+        <v>-10.73267114232066</v>
       </c>
       <c r="F75">
-        <v>-0.1094365931987532</v>
+        <v>0.5467165400283464</v>
       </c>
       <c r="G75">
-        <v>-3.753834481397811</v>
+        <v>-2.706186374568945</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-11.33488942948191</v>
       </c>
       <c r="E76">
-        <v>-11.16389960817508</v>
+        <v>-11.15996436426242</v>
       </c>
       <c r="F76">
-        <v>-0.0557153103923997</v>
+        <v>0.07431600592724709</v>
       </c>
       <c r="G76">
-        <v>-3.292271607073841</v>
+        <v>-2.325633579326106</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-11.18493586748954</v>
       </c>
       <c r="E77">
-        <v>-10.82451765214423</v>
+        <v>-12.35073113305334</v>
       </c>
       <c r="F77">
-        <v>0.3663917252151304</v>
+        <v>-0.502627807876761</v>
       </c>
       <c r="G77">
-        <v>-2.926730400465463</v>
+        <v>-3.893220773243022</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-11.0396897504152</v>
       </c>
       <c r="E78">
-        <v>-11.95118387135659</v>
+        <v>-11.13830920155774</v>
       </c>
       <c r="F78">
-        <v>0.03755554569321343</v>
+        <v>0.2001880895174376</v>
       </c>
       <c r="G78">
-        <v>-3.431008217050283</v>
+        <v>-4.075597629960079</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.89890970717756</v>
       </c>
       <c r="E79">
-        <v>-12.23634187961959</v>
+        <v>-13.5271109399219</v>
       </c>
       <c r="F79">
-        <v>0.05091214169595266</v>
+        <v>-0.428749861058087</v>
       </c>
       <c r="G79">
-        <v>-2.87633739975551</v>
+        <v>-3.170584224320275</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.76146410038716</v>
       </c>
       <c r="E80">
-        <v>-12.31606566452463</v>
+        <v>-13.38219071472844</v>
       </c>
       <c r="F80">
-        <v>0.08394246351518014</v>
+        <v>-0.7103061426978194</v>
       </c>
       <c r="G80">
-        <v>-2.287348286170506</v>
+        <v>-2.188419456153247</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.62273951723485</v>
       </c>
       <c r="E81">
-        <v>-13.18933659216378</v>
+        <v>-14.10848548997464</v>
       </c>
       <c r="F81">
-        <v>-0.2373688265197061</v>
+        <v>-0.6327651552239661</v>
       </c>
       <c r="G81">
-        <v>-2.496539285471344</v>
+        <v>-1.858463097357046</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.47826037662479</v>
       </c>
       <c r="E82">
-        <v>-13.92704312190931</v>
+        <v>-14.39701268289935</v>
       </c>
       <c r="F82">
-        <v>-0.1883592975004761</v>
+        <v>0.07086337059237875</v>
       </c>
       <c r="G82">
-        <v>-1.524264119084483</v>
+        <v>-1.599748621059509</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.33016935931072</v>
       </c>
       <c r="E83">
-        <v>-14.93342401452992</v>
+        <v>-16.10388963434447</v>
       </c>
       <c r="F83">
-        <v>0.1529935134777413</v>
+        <v>-0.2866989337238194</v>
       </c>
       <c r="G83">
-        <v>-1.507208329418489</v>
+        <v>-1.507611919670301</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.17928417228915</v>
       </c>
       <c r="E84">
-        <v>-15.48331661328134</v>
+        <v>-16.54318784088055</v>
       </c>
       <c r="F84">
-        <v>0.167009489933109</v>
+        <v>0.7120702707707669</v>
       </c>
       <c r="G84">
-        <v>-0.9668698878953715</v>
+        <v>-1.048792146570028</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.02383524181431</v>
       </c>
       <c r="E85">
-        <v>-17.1856741476668</v>
+        <v>-18.47896103951738</v>
       </c>
       <c r="F85">
-        <v>0.104382429179258</v>
+        <v>-0.3173137361964836</v>
       </c>
       <c r="G85">
-        <v>-0.8180139906296026</v>
+        <v>1.165937250629931</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.862817803056439</v>
       </c>
       <c r="E86">
-        <v>-17.25373711200209</v>
+        <v>-19.14783023587231</v>
       </c>
       <c r="F86">
-        <v>0.215192308284345</v>
+        <v>0.1064881391171743</v>
       </c>
       <c r="G86">
-        <v>-0.6009579032507751</v>
+        <v>0.7494189858740193</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.694862740104794</v>
       </c>
       <c r="E87">
-        <v>-18.61721082249755</v>
+        <v>-19.30051679398893</v>
       </c>
       <c r="F87">
-        <v>0.2201227510658077</v>
+        <v>0.1299450188622479</v>
       </c>
       <c r="G87">
-        <v>-0.4434887993914638</v>
+        <v>1.270778841897309</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.517578878802414</v>
       </c>
       <c r="E88">
-        <v>-20.95129048095302</v>
+        <v>-22.46776774274564</v>
       </c>
       <c r="F88">
-        <v>-0.1132363144753946</v>
+        <v>0.08031918449533511</v>
       </c>
       <c r="G88">
-        <v>0.03358112802244122</v>
+        <v>1.613164467960687</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.334070580235347</v>
       </c>
       <c r="E89">
-        <v>-21.59078799489421</v>
+        <v>-20.89391471527584</v>
       </c>
       <c r="F89">
-        <v>0.3726831756393926</v>
+        <v>0.2152072188975954</v>
       </c>
       <c r="G89">
-        <v>0.5169050637286479</v>
+        <v>1.959379279583937</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.151146530935268</v>
       </c>
       <c r="E90">
-        <v>-23.03603688902018</v>
+        <v>-24.00254909647727</v>
       </c>
       <c r="F90">
-        <v>0.392434767991744</v>
+        <v>0.4712091945283658</v>
       </c>
       <c r="G90">
-        <v>0.8754014876488991</v>
+        <v>1.488983356821942</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.971378112351097</v>
       </c>
       <c r="E91">
-        <v>-24.97064626983703</v>
+        <v>-25.98029672069119</v>
       </c>
       <c r="F91">
-        <v>0.2791861752528152</v>
+        <v>0.2577223474788772</v>
       </c>
       <c r="G91">
-        <v>0.7671408635165802</v>
+        <v>1.731527973274536</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.796930471638259</v>
       </c>
       <c r="E92">
-        <v>-26.68380421473079</v>
+        <v>-27.74289201632668</v>
       </c>
       <c r="F92">
-        <v>0.09047082701664305</v>
+        <v>0.1726291343937008</v>
       </c>
       <c r="G92">
-        <v>0.5209672160192405</v>
+        <v>1.708592234574017</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.629659589218948</v>
       </c>
       <c r="E93">
-        <v>-28.67706639089499</v>
+        <v>-27.37562824583061</v>
       </c>
       <c r="F93">
-        <v>0.242651030952343</v>
+        <v>0.3279985528301789</v>
       </c>
       <c r="G93">
-        <v>0.9332658298497067</v>
+        <v>1.389644374109753</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.467135070227039</v>
       </c>
       <c r="E94">
-        <v>-30.04904231133985</v>
+        <v>-30.94039769992863</v>
       </c>
       <c r="F94">
-        <v>0.06522964388593931</v>
+        <v>0.1570226925249581</v>
       </c>
       <c r="G94">
-        <v>1.292661308477246</v>
+        <v>0.9322519323878383</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.309783509926763</v>
       </c>
       <c r="E95">
-        <v>-32.75486213684799</v>
+        <v>-32.13312076949088</v>
       </c>
       <c r="F95">
-        <v>-0.1306900156523801</v>
+        <v>-0.8308584508272315</v>
       </c>
       <c r="G95">
-        <v>1.405906108158361</v>
+        <v>0.5182700518973768</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-8.163093188345583</v>
       </c>
       <c r="E96">
-        <v>-34.46989486998092</v>
+        <v>-34.04151481427733</v>
       </c>
       <c r="F96">
-        <v>-0.265294748402883</v>
+        <v>-0.4691750186821058</v>
       </c>
       <c r="G96">
-        <v>1.129413973451752</v>
+        <v>2.127830632002709</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-8.026931698131799</v>
       </c>
       <c r="E97">
-        <v>-35.63927365603362</v>
+        <v>-36.5742563632123</v>
       </c>
       <c r="F97">
-        <v>-0.1070401263024543</v>
+        <v>-0.6144433250088467</v>
       </c>
       <c r="G97">
-        <v>1.644172011697439</v>
+        <v>2.987546774014379</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.899878080734394</v>
       </c>
       <c r="E98">
-        <v>-38.73134061507798</v>
+        <v>-38.49610903274954</v>
       </c>
       <c r="F98">
-        <v>-0.4868225578313464</v>
+        <v>-0.1757689413453264</v>
       </c>
       <c r="G98">
-        <v>0.1449851624087082</v>
+        <v>2.172461807654277</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.779711646136431</v>
       </c>
       <c r="E99">
-        <v>-39.94904048302953</v>
+        <v>-41.20793814326586</v>
       </c>
       <c r="F99">
-        <v>-0.2085259019216301</v>
+        <v>-1.497177308821487</v>
       </c>
       <c r="G99">
-        <v>0.6479931462500237</v>
+        <v>1.134516272976689</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.661468908721161</v>
       </c>
       <c r="E100">
-        <v>-43.11235618787357</v>
+        <v>-44.55655221179276</v>
       </c>
       <c r="F100">
-        <v>-0.4238036792959712</v>
+        <v>-0.6956274723202122</v>
       </c>
       <c r="G100">
-        <v>0.6893595064499433</v>
+        <v>1.147992249921328</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.541321996639442</v>
       </c>
       <c r="E101">
-        <v>-44.50986364477368</v>
+        <v>-46.67925628899221</v>
       </c>
       <c r="F101">
-        <v>-0.61268967121712</v>
+        <v>-0.8549324642873907</v>
       </c>
       <c r="G101">
-        <v>0.6832728404571733</v>
+        <v>-0.7181434500247837</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.421249413416842</v>
       </c>
       <c r="E102">
-        <v>-47.4262031699504</v>
+        <v>-48.46227953087631</v>
       </c>
       <c r="F102">
-        <v>-0.8156429983726101</v>
+        <v>-1.217088065852112</v>
       </c>
       <c r="G102">
-        <v>0.0974566681201515</v>
+        <v>1.282030150624645</v>
       </c>
     </row>
   </sheetData>
